--- a/data/600006_东风汽车_财务数据.xlsx
+++ b/data/600006_东风汽车_财务数据.xlsx
@@ -11138,7 +11138,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -18147,7 +18147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18177,8 +18177,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18225,22 +18223,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -18250,75 +18248,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -18352,58 +18340,52 @@
         <v>7.387466620458448</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>0.007169516090911553</v>
+      <c r="J2" s="3" t="n">
+        <v>65.54289700069751</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>65.54289700069751</v>
-      </c>
-      <c r="L2" s="3" t="n">
         <v>1.129928172386273</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.9854748603351957</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>190.2159244264508</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>2.187357771076062</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>164.5821295264832</v>
-      </c>
-      <c r="P2" s="3" t="n">
         <v>8.985493920878453</v>
       </c>
+      <c r="P2" s="6" t="n">
+        <v>0.7448510094205999</v>
+      </c>
       <c r="Q2" s="3" t="n">
-        <v>40.06457554475816</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0.7448510094205999</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.131375968186891</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="3" t="n">
+        <v>10.58490279983553</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>81000000</v>
+      </c>
       <c r="X2" s="3" t="n">
-        <v>10.58490279983553</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>81000000</v>
+        <v>1.112309694635377</v>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>1.112309694635377</v>
+        <v>1.419159019028157</v>
       </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.419159019028157</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18439,64 +18421,58 @@
       <c r="I3" s="3" t="n">
         <v>3.339482851009013</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>-0.06238724382701287</v>
+      <c r="J3" s="3" t="n">
+        <v>60.51270519451315</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>60.51270519451315</v>
+        <v>1.340701958503006</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.340701958503006</v>
+        <v>1.181500872600349</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.181500872600349</v>
+        <v>153.246013667426</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>2.413408634955822</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>149.1666163722787</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>10.93851768344728</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.9315082930226758</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>32.91122347818392</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.9315082930226758</v>
-      </c>
+        <v>1.307859478229829</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.307859478229829</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>14.25180256240261</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-223.154414214457</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>14.25180256240261</v>
+        <v>-17.28435247616833</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>-223.154414214457</v>
+        <v>4.233788540471627</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-17.28435247616833</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>4.233788540471627</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-783000000</v>
       </c>
-      <c r="Z3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>0.9227426299612698</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>1.95580066905945</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.95580066905945</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18532,64 +18508,58 @@
       <c r="I4" s="3" t="n">
         <v>3.408111570504742</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>-0.2013441335267484</v>
+      <c r="J4" s="3" t="n">
+        <v>61.98675496688742</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>61.98675496688742</v>
+        <v>1.32343857240906</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.32343857240906</v>
+        <v>1.166094715168154</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.166094715168154</v>
+        <v>163.0880579010856</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1.632031620001132</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>220.583961479711</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>8.254752089735327</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>43.61124308598621</v>
-      </c>
-      <c r="R4" s="6" t="n">
+      <c r="P4" s="6" t="n">
         <v>0.7707857926308194</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>0.9858912555089903</v>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="3" t="n">
+        <v>-21.20251472430795</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>734.9810147997342</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>-21.20251472430795</v>
+        <v>10.35529570496964</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>734.9810147997342</v>
+        <v>-1.151342179574223</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>10.35529570496964</v>
+        <v>-990000000</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-1.151342179574223</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>-990000000</v>
+        <v>1.058275437648342</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.058275437648342</v>
+        <v>1.741292102922944</v>
       </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>1.741292102922944</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18625,64 +18595,58 @@
       <c r="I5" s="3" t="n">
         <v>3.579406987416912</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>-0.3256421389679874</v>
+      <c r="J5" s="3" t="n">
+        <v>59.11047345767575</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>59.11047345767575</v>
+        <v>1.36407445903808</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.36407445903808</v>
+        <v>1.145610885382217</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.145610885382217</v>
+        <v>144.5614035087719</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>1.700111992206224</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>211.7507562150834</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>6.544046953762662</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>55.01183022426345</v>
-      </c>
-      <c r="R5" s="6" t="n">
+      <c r="P5" s="6" t="n">
         <v>0.7032765803022185</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0.9055080448744224</v>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
+        <v>-6.244461505784417</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-24.6554551880496</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>-6.244461505784417</v>
+        <v>-4.13143148242486</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-24.6554551880496</v>
+        <v>1.228285248071002</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-4.13143148242486</v>
+        <v>161000000</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>1.228285248071002</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>161000000</v>
+        <v>1.382308108178314</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>1.382308108178314</v>
+        <v>1.812541690811591</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>1.812541690811591</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18718,64 +18682,58 @@
       <c r="I6" s="3" t="n">
         <v>2.816379045943586</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>-0.4787790331092839</v>
+      <c r="J6" s="3" t="n">
+        <v>59.86708327133859</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>59.86708327133859</v>
+        <v>1.362145390070922</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.362145390070922</v>
+        <v>1.138031914893617</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.138031914893617</v>
+        <v>149.1720217498764</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>2.543929128231917</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>141.5133762984221</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>5.507871544012397</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>65.36100145461013</v>
-      </c>
-      <c r="R6" s="6" t="n">
+      <c r="P6" s="6" t="n">
         <v>0.7046021958216613</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.9216738632099594</v>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="3" t="n">
+        <v>1.577356232935626</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>33.68695624037689</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>1.577356232935626</v>
+        <v>7.14171847600829</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>33.68695624037689</v>
+        <v>2.602599141008388</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>7.14171847600829</v>
+        <v>1142000000</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>2.602599141008388</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>1142000000</v>
+        <v>1.259629679327799</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.259629679327799</v>
+        <v>1.771094898828718</v>
       </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.771094898828718</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18811,64 +18769,58 @@
       <c r="I7" s="3" t="n">
         <v>2.760728529561034</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>-0.5460192742822011</v>
+      <c r="J7" s="3" t="n">
+        <v>58.26878583643497</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>58.26878583643497</v>
+        <v>1.411397709283919</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.411397709283919</v>
+        <v>1.198249371449856</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.198249371449856</v>
+        <v>139.6287814872846</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>3.613766467638857</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>99.61905486250606</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>6.400869835042558</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.7766281488450493</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>56.2423560043549</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.7766281488450493</v>
-      </c>
+        <v>1.018939591786252</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.018939591786252</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>13.22786437782285</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-30.87278312923816</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>13.22786437782285</v>
+        <v>-1.393641819173734</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>-30.87278312923816</v>
+        <v>2.564032299487551</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>-1.393641819173734</v>
+        <v>797000000.0000001</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>2.564032299487551</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>797000000.0000001</v>
+        <v>1.26166901473617</v>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>1.26166901473617</v>
+        <v>1.918373986284356</v>
       </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>1.918373986284356</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18905,63 +18857,57 @@
         <v>3.378302983343117</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-1.355254945209575</v>
+        <v>52.04116250141355</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>52.04116250141355</v>
+        <v>1.597125748502994</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.597125748502994</v>
+        <v>1.419161676646707</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.419161676646707</v>
+        <v>108.5121433624145</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>3.087246369864506</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>116.6087693920585</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>6.513140181981457</v>
       </c>
-      <c r="Q8" s="3" t="n">
-        <v>55.27287758920601</v>
-      </c>
-      <c r="R8" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.648956148392781</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.8556482147481838</v>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>-21.60795369822742</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-22.85757189061252</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>-21.60795369822742</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-22.85757189061252</v>
+        <v>-11.04516648224525</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>-0.9835628336889767</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-11.04516648224525</v>
-      </c>
-      <c r="X8" s="6" t="n">
-        <v>-0.9835628336889767</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>-493000000</v>
       </c>
+      <c r="X8" s="3" t="n">
+        <v>1.228056560015137</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
+      </c>
       <c r="Z8" s="3" t="n">
-        <v>1.228056560015137</v>
+        <v>2.07576989302373</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>2.07576989302373</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18998,63 +18944,57 @@
         <v>2.970657653746642</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-1.192312205068248</v>
+        <v>55.15334863342374</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>55.15334863342374</v>
+        <v>1.501798746017063</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.501798746017063</v>
+        <v>1.299414122725871</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1.299414122725871</v>
+        <v>122.9820888578739</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>3.117651358796332</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>115.4715388506396</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>7.34954150197974</v>
       </c>
-      <c r="Q9" s="3" t="n">
-        <v>48.98264740773654</v>
-      </c>
-      <c r="R9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>0.6549453163807043</v>
       </c>
+      <c r="Q9" s="6" t="n">
+        <v>0.8637769517715674</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="6" t="n">
-        <v>0.8637769517715674</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="6" t="n">
         <v>-0.9844555514162601</v>
       </c>
+      <c r="T9" s="3" t="n">
+        <v>-31.16972435866987</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>8.402125975347733</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>-31.16972435866987</v>
+        <v>-1.310708873101694</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>8.402125975347733</v>
+        <v>-469000000</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-1.310708873101694</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>-469000000</v>
+        <v>1.15517934922903</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.15517934922903</v>
+        <v>1.874664041291453</v>
       </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>1.874664041291453</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19090,64 +19030,58 @@
       <c r="I10" s="3" t="n">
         <v>3.93448288926995</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>-0.7773972998816204</v>
+      <c r="J10" s="3" t="n">
+        <v>50.27563395810364</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>50.27563395810364</v>
+        <v>1.586505644526122</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.586505644526122</v>
+        <v>1.388684694145445</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.388684694145445</v>
+        <v>101.1086474501109</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>2.854937641905507</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>126.0973251099525</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>6.895106022226697</v>
       </c>
-      <c r="Q10" s="3" t="n">
-        <v>52.21094481209182</v>
-      </c>
-      <c r="R10" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>0.6008661505914022</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>0.8193629326246394</v>
       </c>
-      <c r="T10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="3" t="n">
+        <v>-9.38460917424135</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-83.51958504202743</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>-9.38460917424135</v>
+        <v>-10.11370749008971</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-83.51958504202743</v>
+        <v>-76.39190931560277</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-10.11370749008971</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-76.39190931560277</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>-3171000000</v>
       </c>
-      <c r="Z10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.9877239792067759</v>
       </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>1.999194858563396</v>
+      </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.999194858563396</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19183,64 +19117,58 @@
       <c r="I11" s="3" t="n">
         <v>4.197187031029581</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.2009305038089685</v>
+      <c r="J11" s="3" t="n">
+        <v>49.38302536799248</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>49.38302536799248</v>
+        <v>1.495527986151183</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.495527986151183</v>
+        <v>1.317801500288517</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.317801500288517</v>
+        <v>97.56218289815617</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.923935382644</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>123.1217359100686</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>7.309039766279664</v>
       </c>
-      <c r="Q11" s="3" t="n">
-        <v>49.25407598148036</v>
-      </c>
-      <c r="R11" s="6" t="n">
+      <c r="P11" s="6" t="n">
         <v>0.5336503549442737</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>0.789031509528348</v>
       </c>
-      <c r="T11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="3" t="n">
+        <v>-19.01027042994565</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-1530.167006404509</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>-19.01027042994565</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>-1530.167006404509</v>
+        <v>-7.357975976324493</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0.4160282116719749</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-7.357975976324493</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>0.4160282116719749</v>
-      </c>
-      <c r="Y11" s="3" t="n">
         <v>-981000000</v>
       </c>
+      <c r="X11" s="3" t="n">
+        <v>1.051019934828573</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="n">
-        <v>1.051019934828573</v>
+        <v>1.782261858381086</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.782261858381086</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
